--- a/Outputs/Scenarios/PtX_demand_DE_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DE_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.02207968662960989</v>
       </c>
       <c r="K16" t="n">
-        <v>0.009835277510041367</v>
+        <v>0.01269466743197721</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.002008959093482734</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01967055502008273</v>
+        <v>0.01607167274786188</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>0.0003181309096915025</v>
       </c>
       <c r="K28" t="n">
-        <v>0.003278425836680456</v>
+        <v>0.002008959093482734</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.03268628793279557</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05240804800331547</v>
+        <v>0.06764453158357187</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0107048961760813</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1048160960066309</v>
+        <v>0.08563916940865043</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.001720330943831346</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01746934933443849</v>
+        <v>0.0107048961760813</v>
       </c>
     </row>
     <row r="43">
